--- a/ExcelTool/UIPageData.xlsx
+++ b/ExcelTool/UIPageData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="12060"/>
+    <workbookView windowWidth="26940" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="UIPageData" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>idx</t>
   </si>
@@ -328,6 +328,15 @@
   </si>
   <si>
     <t>保存游戏UI</t>
+  </si>
+  <si>
+    <t>SetDatingTargetUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/SetDatingTargetUI/SetDatingTargetUI.prefab</t>
+  </si>
+  <si>
+    <t>开始约会UI</t>
   </si>
 </sst>
 </file>
@@ -335,10 +344,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -378,6 +387,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -385,7 +416,53 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -407,14 +484,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -428,78 +514,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,14 +525,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -547,37 +556,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,145 +730,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,6 +775,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -776,6 +809,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -796,34 +838,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -838,21 +862,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -861,10 +870,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -873,133 +882,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1718,12 +1727,28 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="3:7">
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" spans="3:7">
       <c r="C16" s="4"/>

--- a/ExcelTool/UIPageData.xlsx
+++ b/ExcelTool/UIPageData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26940" windowHeight="12060"/>
+    <workbookView windowWidth="21000" windowHeight="16310"/>
   </bookViews>
   <sheets>
     <sheet name="UIPageData" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>idx</t>
   </si>
@@ -337,6 +337,15 @@
   </si>
   <si>
     <t>开始约会UI</t>
+  </si>
+  <si>
+    <t>InventoryUI</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/InventoryUI/InventoryUI.prefab</t>
+  </si>
+  <si>
+    <t>背包界面UI</t>
   </si>
 </sst>
 </file>
@@ -344,10 +353,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -387,7 +396,83 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -402,28 +487,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -431,9 +495,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -462,22 +526,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -485,46 +534,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -556,187 +565,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,11 +774,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -789,39 +828,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -837,17 +843,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -862,6 +862,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -870,145 +879,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1750,12 +1759,28 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="3:7">
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="17" spans="3:7">
       <c r="C17" s="4"/>

--- a/ExcelTool/UIPageData.xlsx
+++ b/ExcelTool/UIPageData.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="16310"/>
+    <workbookView windowWidth="23910" windowHeight="16310"/>
   </bookViews>
   <sheets>
     <sheet name="UIPageData" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -190,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
   <si>
     <t>idx</t>
   </si>
@@ -346,6 +344,27 @@
   </si>
   <si>
     <t>背包界面UI</t>
+  </si>
+  <si>
+    <t>GameSettlePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/CommonUI/GameSettlePanel.prefab</t>
+  </si>
+  <si>
+    <t>等待补充</t>
+  </si>
+  <si>
+    <t>KitchenPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/MiniGame1KitchenUI/KitchenPanel.prefab</t>
+  </si>
+  <si>
+    <t>CrashSprintPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/CasinoGameUI/CrashSprintPanel.prefab</t>
   </si>
 </sst>
 </file>
@@ -353,10 +372,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -396,67 +415,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -472,14 +430,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -487,15 +437,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -518,7 +460,84 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -565,7 +584,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,13 +650,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,19 +704,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,133 +758,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -774,17 +793,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -794,21 +807,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -828,6 +826,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -843,11 +856,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -879,10 +898,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -891,73 +910,73 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -966,58 +985,58 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1782,33 +1801,97 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="3:7">
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="3:7">
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="3:7">
-      <c r="C19" s="4"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="3:7">
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="21" spans="3:7">
       <c r="C21" s="4"/>
@@ -3069,28 +3152,4 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/ExcelTool/UIPageData.xlsx
+++ b/ExcelTool/UIPageData.xlsx
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>idx</t>
   </si>
@@ -346,13 +346,58 @@
     <t>背包界面UI</t>
   </si>
   <si>
+    <t>CrashSprintPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/CasinoGameUI/CrashSprintPanel.prefab</t>
+  </si>
+  <si>
+    <t>爆点冲刺面板</t>
+  </si>
+  <si>
     <t>GameSettlePanel</t>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/CommonUI/GameSettlePanel.prefab</t>
   </si>
   <si>
-    <t>等待补充</t>
+    <t>游戏结算面板</t>
+  </si>
+  <si>
+    <t>FactoryMaterialSelectPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Factory/FactoryMaterialSelectPanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂材料选择面板</t>
+  </si>
+  <si>
+    <t>FactoryProductSelectPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Factory/FactoryProductSelectPanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂产品选择面板</t>
+  </si>
+  <si>
+    <t>FactoryMainPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/Factory/FactoryMainPanel.prefab</t>
+  </si>
+  <si>
+    <t>工厂主面板</t>
+  </si>
+  <si>
+    <t>CasinoGameEnterPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/CasinoGameUI/CasinoGameEnterPanel.prefab</t>
+  </si>
+  <si>
+    <t>赌场游戏进入面板</t>
   </si>
   <si>
     <t>KitchenPanel</t>
@@ -361,10 +406,16 @@
     <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/MiniGame1KitchenUI/KitchenPanel.prefab</t>
   </si>
   <si>
-    <t>CrashSprintPanel</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/CasinoGameUI/CrashSprintPanel.prefab</t>
+    <t>厨房面板</t>
+  </si>
+  <si>
+    <t>WitchPoisonPanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/CasinoGameUI/WitchPoisonPanel.prefab</t>
+  </si>
+  <si>
+    <t>女巫毒药面板</t>
   </si>
 </sst>
 </file>
@@ -373,9 +424,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -415,14 +466,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -436,8 +517,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -460,7 +557,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -481,55 +593,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -538,21 +604,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -569,7 +620,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -578,31 +629,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,25 +653,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,25 +677,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -680,13 +719,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,49 +773,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,12 +810,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -793,11 +838,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,17 +877,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -856,6 +910,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -870,26 +935,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -898,10 +943,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -910,137 +955,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1058,9 +1103,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1419,11 +1461,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="21.7272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.7272727272727" style="1" customWidth="1"/>
     <col min="3" max="3" width="91" style="2" customWidth="1"/>
     <col min="4" max="4" width="12" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.36363636363636" style="2" customWidth="1"/>
@@ -1844,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1852,12 +1894,12 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="6">
+      <c r="C19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="3">
         <v>0</v>
       </c>
       <c r="E19" s="4">
@@ -1867,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1875,12 +1917,12 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="4">
+        <v>61</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="3">
         <v>0</v>
       </c>
       <c r="E20" s="4">
@@ -1890,131 +1932,195 @@
         <v>0</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="3:7">
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="3:7">
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="3:7">
-      <c r="C23" s="7"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="3:7">
-      <c r="C24" s="7"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="25" spans="3:7">
-      <c r="C25" s="7"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="3:7">
-      <c r="C26" s="7"/>
+      <c r="C26" s="6"/>
       <c r="D26" s="7"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
     <row r="27" spans="3:7">
-      <c r="C27" s="7"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="7"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
     <row r="28" spans="3:7">
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="3:7">
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
     </row>
     <row r="30" spans="3:7">
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
     </row>
     <row r="31" spans="3:7">
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
     </row>
     <row r="32" spans="3:7">
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
     </row>
     <row r="33" spans="3:7">
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
     </row>
     <row r="34" spans="3:7">
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
     </row>
     <row r="35" spans="3:7">
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
     </row>
     <row r="36" spans="3:7">
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
     </row>
     <row r="37" spans="3:7">
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
     </row>
     <row r="38" spans="3:7">
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -2048,1103 +2154,1075 @@
       <c r="G42" s="4"/>
     </row>
     <row r="43" spans="3:7">
-      <c r="C43" s="8"/>
-      <c r="D43" s="9"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="8"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
     </row>
     <row r="44" spans="3:7">
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="8"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
     </row>
     <row r="45" spans="3:7">
-      <c r="C45" s="8"/>
-      <c r="D45" s="9"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="8"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
     </row>
     <row r="46" spans="3:7">
-      <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
     </row>
     <row r="47" spans="3:7">
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="8"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
     </row>
     <row r="48" spans="3:7">
-      <c r="C48" s="8"/>
-      <c r="D48" s="9"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="8"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
     </row>
     <row r="49" spans="3:7">
-      <c r="C49" s="8"/>
-      <c r="D49" s="9"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="G49" s="7"/>
     </row>
     <row r="50" spans="3:7">
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
+      <c r="G50" s="7"/>
     </row>
     <row r="51" spans="3:7">
-      <c r="C51" s="8"/>
-      <c r="D51" s="9"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="8"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
+      <c r="G51" s="7"/>
     </row>
     <row r="52" spans="3:7">
-      <c r="C52" s="8"/>
-      <c r="D52" s="9"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="8"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
+      <c r="G52" s="7"/>
     </row>
     <row r="53" spans="3:7">
-      <c r="C53" s="8"/>
-      <c r="D53" s="9"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="8"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="8"/>
+      <c r="G53" s="7"/>
     </row>
     <row r="54" spans="3:7">
-      <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
-      <c r="G54" s="8"/>
+      <c r="G54" s="7"/>
     </row>
     <row r="55" spans="3:7">
-      <c r="C55" s="8"/>
-      <c r="D55" s="9"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="8"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
-      <c r="G55" s="8"/>
+      <c r="G55" s="7"/>
     </row>
     <row r="56" spans="3:7">
-      <c r="C56" s="8"/>
-      <c r="D56" s="9"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="8"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="8"/>
+      <c r="G56" s="7"/>
     </row>
     <row r="57" spans="3:7">
-      <c r="C57" s="8"/>
-      <c r="D57" s="9"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="8"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="8"/>
+      <c r="G57" s="7"/>
     </row>
     <row r="58" spans="3:7">
-      <c r="C58" s="8"/>
-      <c r="D58" s="9"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="8"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
-      <c r="G58" s="8"/>
+      <c r="G58" s="7"/>
     </row>
     <row r="59" spans="3:7">
-      <c r="C59" s="8"/>
-      <c r="D59" s="9"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="8"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
-      <c r="G59" s="8"/>
+      <c r="G59" s="7"/>
     </row>
     <row r="60" spans="3:7">
-      <c r="C60" s="8"/>
-      <c r="D60" s="9"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="8"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-      <c r="G60" s="8"/>
+      <c r="G60" s="7"/>
     </row>
     <row r="61" spans="3:7">
-      <c r="C61" s="8"/>
-      <c r="D61" s="9"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="8"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-      <c r="G61" s="8"/>
+      <c r="G61" s="7"/>
     </row>
     <row r="62" spans="3:7">
-      <c r="C62" s="8"/>
-      <c r="D62" s="9"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="8"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="8"/>
+      <c r="G62" s="7"/>
     </row>
     <row r="63" spans="3:7">
-      <c r="C63" s="8"/>
-      <c r="D63" s="9"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="8"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
-      <c r="G63" s="8"/>
+      <c r="G63" s="7"/>
     </row>
     <row r="64" spans="3:7">
-      <c r="C64" s="8"/>
-      <c r="D64" s="9"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="8"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-      <c r="G64" s="8"/>
+      <c r="G64" s="7"/>
     </row>
     <row r="65" spans="3:7">
-      <c r="C65" s="8"/>
-      <c r="D65" s="9"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="8"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-      <c r="G65" s="8"/>
+      <c r="G65" s="7"/>
     </row>
     <row r="66" spans="3:7">
-      <c r="C66" s="8"/>
-      <c r="D66" s="9"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="8"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="8"/>
+      <c r="G66" s="7"/>
     </row>
     <row r="67" spans="3:7">
-      <c r="C67" s="8"/>
-      <c r="D67" s="9"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="8"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-      <c r="G67" s="8"/>
+      <c r="G67" s="7"/>
     </row>
     <row r="68" spans="3:7">
-      <c r="C68" s="8"/>
-      <c r="D68" s="9"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="8"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="G68" s="8"/>
+      <c r="G68" s="7"/>
     </row>
     <row r="69" spans="3:7">
-      <c r="C69" s="8"/>
-      <c r="D69" s="9"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="8"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-      <c r="G69" s="8"/>
+      <c r="G69" s="7"/>
     </row>
     <row r="70" spans="3:7">
-      <c r="C70" s="8"/>
-      <c r="D70" s="9"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="8"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
-      <c r="G70" s="8"/>
+      <c r="G70" s="7"/>
     </row>
     <row r="71" spans="3:7">
-      <c r="C71" s="8"/>
-      <c r="D71" s="9"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="8"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="8"/>
+      <c r="G71" s="7"/>
     </row>
     <row r="72" spans="3:7">
-      <c r="C72" s="8"/>
-      <c r="D72" s="9"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="8"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-      <c r="G72" s="8"/>
+      <c r="G72" s="7"/>
     </row>
     <row r="73" spans="3:7">
-      <c r="C73" s="8"/>
-      <c r="D73" s="9"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="8"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-      <c r="G73" s="8"/>
+      <c r="G73" s="7"/>
     </row>
     <row r="74" spans="3:7">
-      <c r="C74" s="8"/>
-      <c r="D74" s="9"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="8"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
-      <c r="G74" s="8"/>
+      <c r="G74" s="7"/>
     </row>
     <row r="75" spans="3:7">
-      <c r="C75" s="8"/>
-      <c r="D75" s="9"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="8"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
-      <c r="G75" s="8"/>
+      <c r="G75" s="7"/>
     </row>
     <row r="76" spans="3:7">
-      <c r="C76" s="8"/>
-      <c r="D76" s="9"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="8"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
-      <c r="G76" s="8"/>
+      <c r="G76" s="7"/>
     </row>
     <row r="77" spans="3:7">
-      <c r="C77" s="8"/>
-      <c r="D77" s="9"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="8"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
-      <c r="G77" s="8"/>
+      <c r="G77" s="7"/>
     </row>
     <row r="78" spans="3:7">
-      <c r="C78" s="8"/>
-      <c r="D78" s="9"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="8"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
-      <c r="G78" s="8"/>
+      <c r="G78" s="7"/>
     </row>
     <row r="79" spans="3:7">
-      <c r="C79" s="8"/>
-      <c r="D79" s="9"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="8"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
-      <c r="G79" s="8"/>
+      <c r="G79" s="7"/>
     </row>
     <row r="80" spans="3:7">
-      <c r="C80" s="8"/>
-      <c r="D80" s="9"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="8"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
-      <c r="G80" s="8"/>
+      <c r="G80" s="7"/>
     </row>
     <row r="81" spans="3:7">
-      <c r="C81" s="8"/>
-      <c r="D81" s="9"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="8"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
-      <c r="G81" s="8"/>
+      <c r="G81" s="7"/>
     </row>
     <row r="82" spans="3:7">
-      <c r="C82" s="8"/>
-      <c r="D82" s="9"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="8"/>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
-      <c r="G82" s="8"/>
+      <c r="G82" s="7"/>
     </row>
     <row r="83" spans="3:7">
-      <c r="C83" s="8"/>
-      <c r="D83" s="9"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="8"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
-      <c r="G83" s="8"/>
+      <c r="G83" s="7"/>
     </row>
     <row r="84" spans="3:7">
-      <c r="C84" s="8"/>
-      <c r="D84" s="9"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
-      <c r="G84" s="8"/>
+      <c r="G84" s="7"/>
     </row>
     <row r="85" spans="3:7">
-      <c r="C85" s="8"/>
-      <c r="D85" s="9"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="8"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
-      <c r="G85" s="8"/>
+      <c r="G85" s="7"/>
     </row>
     <row r="86" spans="3:7">
-      <c r="C86" s="8"/>
-      <c r="D86" s="9"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="8"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
-      <c r="G86" s="8"/>
+      <c r="G86" s="7"/>
     </row>
     <row r="87" spans="3:7">
-      <c r="C87" s="8"/>
-      <c r="D87" s="9"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="8"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
-      <c r="G87" s="8"/>
+      <c r="G87" s="7"/>
     </row>
     <row r="88" spans="3:7">
-      <c r="C88" s="8"/>
+      <c r="C88" s="7"/>
       <c r="D88" s="8"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
-      <c r="G88" s="8"/>
+      <c r="G88" s="7"/>
     </row>
     <row r="89" spans="3:7">
-      <c r="C89" s="8"/>
-      <c r="D89" s="9"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="8"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
-      <c r="G89" s="8"/>
+      <c r="G89" s="7"/>
     </row>
     <row r="90" spans="3:7">
-      <c r="C90" s="8"/>
-      <c r="D90" s="9"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="8"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
-      <c r="G90" s="8"/>
+      <c r="G90" s="7"/>
     </row>
     <row r="91" spans="3:7">
-      <c r="C91" s="8"/>
-      <c r="D91" s="9"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="8"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
-      <c r="G91" s="8"/>
+      <c r="G91" s="7"/>
     </row>
     <row r="92" spans="3:7">
-      <c r="C92" s="8"/>
-      <c r="D92" s="9"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="8"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
-      <c r="G92" s="8"/>
+      <c r="G92" s="7"/>
     </row>
     <row r="93" spans="3:7">
-      <c r="C93" s="8"/>
-      <c r="D93" s="9"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="8"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
-      <c r="G93" s="8"/>
+      <c r="G93" s="7"/>
     </row>
     <row r="94" spans="3:7">
-      <c r="C94" s="8"/>
-      <c r="D94" s="9"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="8"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
-      <c r="G94" s="8"/>
+      <c r="G94" s="7"/>
     </row>
     <row r="95" spans="3:7">
-      <c r="C95" s="8"/>
-      <c r="D95" s="9"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="8"/>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
-      <c r="G95" s="8"/>
+      <c r="G95" s="7"/>
     </row>
     <row r="96" spans="3:7">
-      <c r="C96" s="8"/>
-      <c r="D96" s="9"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="8"/>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
-      <c r="G96" s="8"/>
+      <c r="G96" s="7"/>
     </row>
     <row r="97" spans="3:7">
-      <c r="C97" s="8"/>
-      <c r="D97" s="9"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="8"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
-      <c r="G97" s="8"/>
+      <c r="G97" s="7"/>
     </row>
     <row r="98" spans="3:7">
-      <c r="C98" s="8"/>
-      <c r="D98" s="9"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="8"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
-      <c r="G98" s="8"/>
+      <c r="G98" s="7"/>
     </row>
     <row r="99" spans="3:7">
-      <c r="C99" s="8"/>
-      <c r="D99" s="9"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="8"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
-      <c r="G99" s="8"/>
+      <c r="G99" s="7"/>
     </row>
     <row r="100" spans="3:7">
-      <c r="C100" s="8"/>
-      <c r="D100" s="9"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="8"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
-      <c r="G100" s="8"/>
+      <c r="G100" s="7"/>
     </row>
     <row r="101" spans="3:7">
-      <c r="C101" s="8"/>
-      <c r="D101" s="9"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="8"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
-      <c r="G101" s="8"/>
+      <c r="G101" s="7"/>
     </row>
     <row r="102" spans="3:7">
-      <c r="C102" s="8"/>
-      <c r="D102" s="9"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="8"/>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
-      <c r="G102" s="8"/>
+      <c r="G102" s="7"/>
     </row>
     <row r="103" spans="3:7">
-      <c r="C103" s="8"/>
-      <c r="D103" s="9"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="8"/>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
-      <c r="G103" s="8"/>
+      <c r="G103" s="7"/>
     </row>
     <row r="104" spans="3:7">
-      <c r="C104" s="8"/>
-      <c r="D104" s="9"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="8"/>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
-      <c r="G104" s="8"/>
+      <c r="G104" s="7"/>
     </row>
     <row r="105" spans="3:7">
-      <c r="C105" s="8"/>
-      <c r="D105" s="9"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="8"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
-      <c r="G105" s="8"/>
+      <c r="G105" s="7"/>
     </row>
     <row r="106" spans="3:7">
-      <c r="C106" s="8"/>
-      <c r="D106" s="9"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="8"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
-      <c r="G106" s="8"/>
+      <c r="G106" s="7"/>
     </row>
     <row r="107" spans="3:7">
-      <c r="C107" s="8"/>
-      <c r="D107" s="9"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="8"/>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
-      <c r="G107" s="8"/>
+      <c r="G107" s="7"/>
     </row>
     <row r="108" spans="3:7">
-      <c r="C108" s="8"/>
-      <c r="D108" s="9"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="8"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
-      <c r="G108" s="8"/>
+      <c r="G108" s="7"/>
     </row>
     <row r="109" spans="3:7">
-      <c r="C109" s="8"/>
-      <c r="D109" s="9"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="8"/>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
-      <c r="G109" s="8"/>
+      <c r="G109" s="7"/>
     </row>
     <row r="110" spans="3:7">
-      <c r="C110" s="8"/>
-      <c r="D110" s="9"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="8"/>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
-      <c r="G110" s="8"/>
+      <c r="G110" s="7"/>
     </row>
     <row r="111" spans="3:7">
-      <c r="C111" s="8"/>
-      <c r="D111" s="9"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="8"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
-      <c r="G111" s="8"/>
+      <c r="G111" s="7"/>
     </row>
     <row r="112" spans="3:7">
-      <c r="C112" s="8"/>
-      <c r="D112" s="9"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="8"/>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
-      <c r="G112" s="8"/>
+      <c r="G112" s="7"/>
     </row>
     <row r="113" spans="3:7">
-      <c r="C113" s="8"/>
-      <c r="D113" s="9"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="8"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
-      <c r="G113" s="8"/>
+      <c r="G113" s="7"/>
     </row>
     <row r="114" spans="3:7">
-      <c r="C114" s="8"/>
-      <c r="D114" s="9"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="8"/>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
-      <c r="G114" s="8"/>
+      <c r="G114" s="7"/>
     </row>
     <row r="115" spans="3:7">
-      <c r="C115" s="8"/>
-      <c r="D115" s="9"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="8"/>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
-      <c r="G115" s="8"/>
+      <c r="G115" s="7"/>
     </row>
     <row r="116" spans="3:7">
-      <c r="C116" s="8"/>
-      <c r="D116" s="9"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="8"/>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
-      <c r="G116" s="8"/>
+      <c r="G116" s="7"/>
     </row>
     <row r="117" spans="3:7">
-      <c r="C117" s="8"/>
-      <c r="D117" s="9"/>
+      <c r="C117" s="7"/>
+      <c r="D117" s="8"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
-      <c r="G117" s="8"/>
+      <c r="G117" s="7"/>
     </row>
     <row r="118" spans="3:7">
-      <c r="C118" s="8"/>
-      <c r="D118" s="9"/>
+      <c r="C118" s="7"/>
+      <c r="D118" s="8"/>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
-      <c r="G118" s="8"/>
+      <c r="G118" s="7"/>
     </row>
     <row r="119" spans="3:7">
-      <c r="C119" s="8"/>
-      <c r="D119" s="9"/>
+      <c r="C119" s="7"/>
+      <c r="D119" s="8"/>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
-      <c r="G119" s="8"/>
+      <c r="G119" s="7"/>
     </row>
     <row r="120" spans="3:7">
-      <c r="C120" s="8"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="4"/>
-      <c r="F120" s="4"/>
-      <c r="G120" s="8"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
     </row>
     <row r="121" spans="3:7">
-      <c r="C121" s="8"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
-      <c r="G121" s="8"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
     </row>
     <row r="122" spans="3:7">
-      <c r="C122" s="8"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="4"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="8"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="7"/>
     </row>
     <row r="123" spans="3:7">
-      <c r="C123" s="8"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="4"/>
-      <c r="F123" s="4"/>
-      <c r="G123" s="8"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
     </row>
     <row r="124" spans="3:7">
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="8"/>
-      <c r="G124" s="8"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="7"/>
     </row>
     <row r="125" spans="3:7">
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
-      <c r="G125" s="8"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
     </row>
     <row r="126" spans="3:7">
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
-      <c r="G126" s="8"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
     </row>
     <row r="127" spans="3:7">
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
+      <c r="G127" s="7"/>
     </row>
     <row r="128" spans="3:7">
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7"/>
+      <c r="G128" s="7"/>
     </row>
     <row r="129" spans="3:7">
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
-      <c r="G129" s="8"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="7"/>
     </row>
     <row r="130" spans="3:7">
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
-      <c r="G130" s="8"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
+      <c r="G130" s="7"/>
     </row>
     <row r="131" spans="3:7">
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7"/>
     </row>
     <row r="132" spans="3:7">
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="8"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="7"/>
     </row>
     <row r="133" spans="3:7">
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="7"/>
     </row>
     <row r="134" spans="3:7">
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="7"/>
     </row>
     <row r="135" spans="3:7">
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
-      <c r="G135" s="8"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+      <c r="G135" s="7"/>
     </row>
     <row r="136" spans="3:7">
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
-      <c r="G136" s="8"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
     </row>
     <row r="137" spans="3:7">
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
-      <c r="G137" s="8"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
     </row>
     <row r="138" spans="3:7">
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
-      <c r="G138" s="8"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
     </row>
     <row r="139" spans="3:7">
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
-      <c r="G139" s="8"/>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
     </row>
     <row r="140" spans="3:7">
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
-      <c r="G140" s="8"/>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7"/>
+      <c r="G140" s="7"/>
     </row>
     <row r="141" spans="3:7">
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
-      <c r="G141" s="8"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="7"/>
     </row>
     <row r="142" spans="3:7">
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
     </row>
     <row r="143" spans="3:7">
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
     </row>
     <row r="144" spans="3:7">
-      <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
-      <c r="G144" s="8"/>
+      <c r="C144" s="7"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="7"/>
+      <c r="G144" s="7"/>
     </row>
     <row r="145" spans="3:7">
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
-      <c r="G145" s="8"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
     </row>
     <row r="146" spans="3:7">
-      <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
-      <c r="G146" s="8"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
     </row>
     <row r="147" spans="3:7">
-      <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
-      <c r="G147" s="8"/>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
     </row>
     <row r="148" spans="3:7">
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
-      <c r="F148" s="8"/>
-      <c r="G148" s="8"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
     </row>
     <row r="149" spans="3:7">
-      <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
-      <c r="F149" s="8"/>
-      <c r="G149" s="8"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
     </row>
     <row r="150" spans="3:7">
-      <c r="C150" s="8"/>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8"/>
-      <c r="F150" s="8"/>
-      <c r="G150" s="8"/>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
+      <c r="G150" s="7"/>
     </row>
     <row r="151" spans="3:7">
-      <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
-      <c r="F151" s="8"/>
-      <c r="G151" s="8"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
     </row>
     <row r="152" spans="3:7">
-      <c r="C152" s="8"/>
-      <c r="D152" s="8"/>
-      <c r="E152" s="8"/>
-      <c r="F152" s="8"/>
-      <c r="G152" s="8"/>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
     </row>
     <row r="153" spans="3:7">
-      <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
-      <c r="E153" s="8"/>
-      <c r="F153" s="8"/>
-      <c r="G153" s="8"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
     </row>
     <row r="154" spans="3:7">
-      <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
-      <c r="F154" s="8"/>
-      <c r="G154" s="8"/>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="7"/>
     </row>
     <row r="155" spans="3:7">
-      <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
-      <c r="F155" s="8"/>
-      <c r="G155" s="8"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
     </row>
     <row r="156" spans="3:7">
-      <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
-      <c r="F156" s="8"/>
-      <c r="G156" s="8"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
     </row>
     <row r="157" spans="3:7">
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
-      <c r="F157" s="8"/>
-      <c r="G157" s="8"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
     </row>
     <row r="158" spans="3:7">
-      <c r="C158" s="8"/>
-      <c r="D158" s="8"/>
-      <c r="E158" s="8"/>
-      <c r="F158" s="8"/>
-      <c r="G158" s="8"/>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
     </row>
     <row r="159" spans="3:7">
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
-      <c r="F159" s="8"/>
-      <c r="G159" s="8"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
     </row>
     <row r="160" spans="3:7">
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
-      <c r="F160" s="8"/>
-      <c r="G160" s="8"/>
+      <c r="C160" s="7"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="7"/>
     </row>
     <row r="161" spans="3:7">
-      <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
-      <c r="F161" s="8"/>
-      <c r="G161" s="8"/>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
+      <c r="G161" s="7"/>
     </row>
     <row r="162" spans="3:7">
-      <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
-      <c r="F162" s="8"/>
-      <c r="G162" s="8"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="7"/>
     </row>
     <row r="163" spans="3:7">
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
-      <c r="G163" s="8"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
     </row>
     <row r="164" spans="3:7">
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
-      <c r="F164" s="8"/>
-      <c r="G164" s="8"/>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="7"/>
     </row>
     <row r="165" spans="3:7">
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
-      <c r="G165" s="8"/>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
     </row>
     <row r="166" spans="3:7">
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
-      <c r="G166" s="8"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
     </row>
     <row r="167" spans="3:7">
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
-      <c r="F167" s="8"/>
-      <c r="G167" s="8"/>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
+      <c r="G167" s="7"/>
     </row>
     <row r="168" spans="3:7">
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
-      <c r="F168" s="8"/>
-      <c r="G168" s="8"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
     </row>
     <row r="169" spans="3:7">
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
-      <c r="F169" s="8"/>
-      <c r="G169" s="8"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="7"/>
     </row>
     <row r="170" spans="3:7">
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
-      <c r="F170" s="8"/>
-      <c r="G170" s="8"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="7"/>
     </row>
     <row r="171" spans="3:7">
-      <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
-      <c r="F171" s="8"/>
-      <c r="G171" s="8"/>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="7"/>
     </row>
     <row r="172" spans="3:7">
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
-      <c r="F172" s="8"/>
-      <c r="G172" s="8"/>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7"/>
+      <c r="G172" s="7"/>
     </row>
     <row r="173" spans="3:7">
-      <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
-      <c r="F173" s="8"/>
-      <c r="G173" s="8"/>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
+      <c r="G173" s="7"/>
     </row>
     <row r="174" spans="3:7">
-      <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
-      <c r="F174" s="8"/>
-      <c r="G174" s="8"/>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
+      <c r="G174" s="7"/>
     </row>
     <row r="175" spans="3:7">
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
-      <c r="F175" s="8"/>
-      <c r="G175" s="8"/>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
+      <c r="G175" s="7"/>
     </row>
     <row r="176" spans="3:7">
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
-      <c r="F176" s="8"/>
-      <c r="G176" s="8"/>
+      <c r="C176" s="7"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
+      <c r="F176" s="7"/>
+      <c r="G176" s="7"/>
     </row>
     <row r="177" spans="3:7">
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="8"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="7"/>
     </row>
     <row r="178" spans="3:7">
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="8"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
     </row>
     <row r="179" spans="3:7">
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
-      <c r="G179" s="8"/>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
+      <c r="G179" s="7"/>
     </row>
     <row r="180" spans="3:7">
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
-      <c r="F180" s="8"/>
-      <c r="G180" s="8"/>
+      <c r="C180" s="7"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="7"/>
+      <c r="F180" s="7"/>
+      <c r="G180" s="7"/>
     </row>
     <row r="181" spans="3:7">
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
-      <c r="F181" s="8"/>
-      <c r="G181" s="8"/>
+      <c r="C181" s="7"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7"/>
+      <c r="G181" s="7"/>
     </row>
     <row r="182" spans="3:7">
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
-      <c r="F182" s="8"/>
-      <c r="G182" s="8"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
+      <c r="G182" s="7"/>
     </row>
     <row r="183" spans="3:7">
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
-      <c r="F183" s="8"/>
-      <c r="G183" s="8"/>
+      <c r="C183" s="7"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="7"/>
+      <c r="F183" s="7"/>
+      <c r="G183" s="7"/>
     </row>
     <row r="184" spans="3:7">
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
-      <c r="F184" s="8"/>
-      <c r="G184" s="8"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="7"/>
     </row>
     <row r="185" spans="3:7">
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
-      <c r="F185" s="8"/>
-      <c r="G185" s="8"/>
+      <c r="C185" s="7"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="7"/>
+      <c r="F185" s="7"/>
+      <c r="G185" s="7"/>
     </row>
     <row r="186" spans="3:7">
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
-      <c r="F186" s="8"/>
-      <c r="G186" s="8"/>
+      <c r="C186" s="7"/>
+      <c r="D186" s="7"/>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
+      <c r="G186" s="7"/>
     </row>
     <row r="187" spans="3:7">
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
-      <c r="F187" s="8"/>
-      <c r="G187" s="8"/>
+      <c r="C187" s="7"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
+      <c r="G187" s="7"/>
     </row>
     <row r="188" spans="3:7">
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
-      <c r="F188" s="8"/>
-      <c r="G188" s="8"/>
+      <c r="C188" s="7"/>
+      <c r="D188" s="7"/>
+      <c r="E188" s="7"/>
+      <c r="F188" s="7"/>
+      <c r="G188" s="7"/>
     </row>
     <row r="189" spans="3:7">
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
-      <c r="F189" s="8"/>
-      <c r="G189" s="8"/>
+      <c r="C189" s="7"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="7"/>
     </row>
     <row r="190" spans="3:7">
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
-      <c r="F190" s="8"/>
-      <c r="G190" s="8"/>
+      <c r="C190" s="7"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
+      <c r="G190" s="7"/>
     </row>
     <row r="191" spans="3:7">
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
-      <c r="G191" s="8"/>
+      <c r="C191" s="7"/>
+      <c r="D191" s="7"/>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="7"/>
     </row>
     <row r="192" spans="3:7">
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
-      <c r="F192" s="8"/>
-      <c r="G192" s="8"/>
+      <c r="C192" s="7"/>
+      <c r="D192" s="7"/>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="7"/>
     </row>
     <row r="193" spans="3:7">
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
-      <c r="F193" s="8"/>
-      <c r="G193" s="8"/>
+      <c r="C193" s="7"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
+      <c r="G193" s="7"/>
     </row>
     <row r="194" spans="3:7">
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
-      <c r="F194" s="8"/>
-      <c r="G194" s="8"/>
+      <c r="C194" s="7"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
+      <c r="G194" s="7"/>
     </row>
     <row r="195" spans="3:7">
-      <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8"/>
-      <c r="F195" s="8"/>
-      <c r="G195" s="8"/>
-    </row>
-    <row r="196" spans="3:7">
-      <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
-      <c r="F196" s="8"/>
-      <c r="G196" s="8"/>
-    </row>
-    <row r="197" spans="3:7">
-      <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
-      <c r="E197" s="8"/>
-      <c r="F197" s="8"/>
-      <c r="G197" s="8"/>
-    </row>
-    <row r="198" spans="3:7">
-      <c r="C198" s="8"/>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
-      <c r="F198" s="8"/>
-      <c r="G198" s="8"/>
-    </row>
-    <row r="199" spans="3:7">
-      <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
-      <c r="E199" s="8"/>
-      <c r="F199" s="8"/>
-      <c r="G199" s="8"/>
+      <c r="C195" s="7"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/UIPageData.xlsx
+++ b/ExcelTool/UIPageData.xlsx
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="79">
   <si>
     <t>idx</t>
   </si>
@@ -416,6 +416,15 @@
   </si>
   <si>
     <t>女巫毒药面板</t>
+  </si>
+  <si>
+    <t>PhotoGamePanel</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UGUI/PhotoStudioUI/PhotoGamePanel.prefab</t>
+  </si>
+  <si>
+    <t>拍照</t>
   </si>
 </sst>
 </file>
@@ -423,10 +432,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -466,14 +475,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -487,6 +503,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -494,32 +525,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -534,9 +542,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -563,6 +579,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
@@ -572,38 +612,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -629,6 +638,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -641,163 +668,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -810,6 +687,138 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -834,6 +843,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -863,6 +881,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -873,15 +906,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -920,21 +944,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -943,10 +952,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -955,133 +964,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2027,12 +2036,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="3:7">
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="7">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="26" spans="3:7">
       <c r="C26" s="6"/>

--- a/ExcelTool/UIPageData.xlsx
+++ b/ExcelTool/UIPageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{305F56B0-91EE-4101-9B96-CABAAEFBB2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA9E7D4-0E52-4E7E-A066-7C2F12D27C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4070" yWindow="3550" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>81</v>

--- a/ExcelTool/UIPageData.xlsx
+++ b/ExcelTool/UIPageData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA9E7D4-0E52-4E7E-A066-7C2F12D27C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276CC1ED-8E19-498E-84C7-188DF3DA65D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4070" yWindow="3550" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
